--- a/Cleaned + Pivot.xlsx
+++ b/Cleaned + Pivot.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\DATA SCIENCE\EXCEL\LUX ASSIGNMENTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\datascience\excel\assign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001C6232-B6EC-4198-8BF6-269BAF325753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962BDB4F-C180-4A74-9840-C289095FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{806BCAF3-3F87-4DA0-B6D5-0F0ACE6C1A1A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{806BCAF3-3F87-4DA0-B6D5-0F0ACE6C1A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel_jumia_dataset assignment " sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1226,7 +1226,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1250,7 +1250,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2327,6 +2326,708 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Cleaned + Pivot.xlsx]PIVOT!PivotTable3</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>PRODUCT</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> COUNT BY DISCOUNT %</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KE"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="58000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="86000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:tint val="86000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:tint val="58000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$M$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="58000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-750F-4C56-9FE6-F0C9245FAB6A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="86000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-750F-4C56-9FE6-F0C9245FAB6A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:tint val="86000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-750F-4C56-9FE6-F0C9245FAB6A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:tint val="58000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-750F-4C56-9FE6-F0C9245FAB6A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-KE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$L$44:$L$48</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>HIGH_DISCOUNT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LOW_DISCOUNT</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>MEDIUM_DISCOUNT</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$M$44:$M$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-750F-4C56-9FE6-F0C9245FAB6A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-KE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-KE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -2347,10 +3048,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2358,14 +3056,26 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>RANKING</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> BY PRODUCT RATING</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2384,10 +3094,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5718,15 +6425,15 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="103"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="3"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Cleaned + Pivot.xlsx]PIVOT!PivotTable2</c:name>
-    <c:fmtId val="3"/>
+    <c:name>[Cleaned + Pivot.xlsx]PIVOT!PivotTable4</c:name>
+    <c:fmtId val="6"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -5750,11 +6457,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>TOP</a:t>
+              <a:t>RANKING</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> 10 PRODUCT PERFORMANCE</a:t>
+              <a:t> BY RATING</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5779,6 +6486,397 @@
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-KE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$M$53</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$L$54:$L$58</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>POOR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>EXCELLENT</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>AVERAGE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$M$54:$M$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-32AB-4094-9FC1-C9A0EC437A9F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-KE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-KE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Cleaned + Pivot.xlsx]PIVOT!PivotTable2</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>TOP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> 10 PRODUCT PERFORMANCE</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20549476418540466"/>
+          <c:y val="0.1020971975277284"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -7126,7 +8224,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7149,10 +8247,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -7160,11 +8255,19 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Discount</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> %  to Reviews Correlation</a:t>
             </a:r>
           </a:p>
@@ -7185,10 +8288,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -8132,7 +9232,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8155,10 +9255,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -8166,14 +9263,26 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Rating</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> -Reviews Correlation</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -8192,10 +9301,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -9083,702 +10189,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="103"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="3"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Cleaned + Pivot.xlsx]PIVOT!PivotTable3</c:name>
-    <c:fmtId val="4"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>PRODUCT</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> COUNT BY DISCOUNT %</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KE"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KE"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KE"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="bestFit"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:shade val="58000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:shade val="86000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="9"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:tint val="86000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="10"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:tint val="58000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>PIVOT!$M$43</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:shade val="58000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-750F-4C56-9FE6-F0C9245FAB6A}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:shade val="86000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-750F-4C56-9FE6-F0C9245FAB6A}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:tint val="86000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-750F-4C56-9FE6-F0C9245FAB6A}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:tint val="58000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-750F-4C56-9FE6-F0C9245FAB6A}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-KE"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>PIVOT!$L$44:$L$48</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>HIGH_DISCOUNT</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>LOW_DISCOUNT</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>MEDIUM_DISCOUNT</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>(blank)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>PIVOT!$M$44:$M$48</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-750F-4C56-9FE6-F0C9245FAB6A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="bestFit"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-KE"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-KE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -9820,6 +10230,12 @@
 </file>
 
 <file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10020,12 +10436,6 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10062,6 +10472,12 @@
     <a:lumMod val="50000"/>
     <a:lumOff val="50000"/>
   </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
 
@@ -10106,8 +10522,42 @@
 </file>
 
 <file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -10628,6 +11078,525 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13195,6 +14164,525 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13669,522 +15157,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -14721,7 +15693,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -14748,8 +15720,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -14778,7 +15750,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -14829,13 +15801,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -14846,25 +15811,18 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -14899,7 +15857,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -15220,6 +16178,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -15577,6 +16546,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1970341</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>27241</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>275167</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>9571</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{784D2C60-02E4-7FA7-DF4B-B1219D82D89B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -16012,16 +17017,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16050,16 +17055,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>165101</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>173567</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>529167</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16089,15 +17094,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16126,16 +17131,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>527050</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16164,16 +17169,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>501650</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16213,8 +17218,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>113564</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="category Rating 1">
@@ -16237,7 +17242,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -16291,8 +17296,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>30921</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Discount_category 1">
@@ -16315,7 +17320,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25048,191 +26053,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDB06582-160B-4788-A911-CA10DFC396DA}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="L43:M48" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="PRODUCT COUNT" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB9A0923-9E89-41A8-A68D-33699573BD61}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E18:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B3B400B-9577-4EEF-B566-A92C3E25FD68}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="111">
+      <items count="121">
         <item x="38"/>
         <item x="11"/>
         <item x="0"/>
@@ -25275,6 +26100,12 @@
         <item x="85"/>
         <item x="15"/>
         <item x="63"/>
+        <item x="110"/>
+        <item x="114"/>
+        <item x="112"/>
+        <item x="111"/>
+        <item x="113"/>
+        <item x="115"/>
         <item x="97"/>
         <item x="42"/>
         <item x="77"/>
@@ -25296,6 +26127,8 @@
         <item x="30"/>
         <item x="23"/>
         <item x="10"/>
+        <item x="117"/>
+        <item x="116"/>
         <item x="80"/>
         <item x="61"/>
         <item x="99"/>
@@ -25309,6 +26142,8 @@
         <item x="22"/>
         <item x="103"/>
         <item x="18"/>
+        <item x="119"/>
+        <item x="118"/>
         <item x="76"/>
         <item x="1"/>
         <item x="96"/>
@@ -25346,120 +26181,35 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="92"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="98"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="discount%" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 top="0" val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94B2C9B9-4697-4B48-8B71-6C0F0E2C195F}" name="PivotTable17" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A51:D55" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="24">
+      <items count="43">
+        <item x="38"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="39"/>
+        <item x="23"/>
+        <item x="30"/>
+        <item x="37"/>
+        <item x="36"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="29"/>
         <item x="22"/>
         <item x="15"/>
         <item x="19"/>
@@ -25486,52 +26236,110 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
+    <pivotField dataField="1" showAll="0">
+      <items count="44">
+        <item x="39"/>
+        <item x="41"/>
+        <item x="26"/>
+        <item x="34"/>
+        <item x="24"/>
+        <item x="38"/>
+        <item x="31"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="30"/>
+        <item x="36"/>
+        <item x="27"/>
+        <item x="35"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="40"/>
+        <item x="33"/>
+        <item x="37"/>
+        <item x="29"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
         <item x="1"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="11"/>
         <item x="0"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="23"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="6"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="11">
     <i>
-      <x/>
+      <x v="22"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="40"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="100"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="3">
-    <dataField name="Average_reviews" fld="8" subtotal="average" baseField="6" baseItem="0" numFmtId="2"/>
-    <dataField name="Averag_rating" fld="10" subtotal="average" baseField="6" baseItem="0" numFmtId="164"/>
-    <dataField name="Average Discount %" fld="4" subtotal="average" baseField="6" baseItem="0" numFmtId="10"/>
+  <dataFields count="1">
+    <dataField name="ratings" fld="10" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -25543,7 +26351,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{44F0E56E-6032-4903-B6B8-CC1228051757}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A32:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -25781,8 +26589,119 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F823CBAF-05D0-4137-887E-0DCD631805ED}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22B681EE-FF7B-4954-B4E1-F46FE96FADCE}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="L53:M58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product" fld="0" subtotal="count" baseField="11" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F823CBAF-05D0-4137-887E-0DCD631805ED}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
   <location ref="A59:E70" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -26128,6 +27047,216 @@
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB9A0923-9E89-41A8-A68D-33699573BD61}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E18:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="111">
+        <item x="38"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="31"/>
+        <item x="60"/>
+        <item x="55"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="102"/>
+        <item x="79"/>
+        <item x="5"/>
+        <item x="101"/>
+        <item x="92"/>
+        <item x="47"/>
+        <item x="72"/>
+        <item x="65"/>
+        <item x="64"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="20"/>
+        <item x="95"/>
+        <item x="12"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="57"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="59"/>
+        <item x="107"/>
+        <item x="91"/>
+        <item x="45"/>
+        <item x="75"/>
+        <item x="70"/>
+        <item x="98"/>
+        <item x="100"/>
+        <item x="66"/>
+        <item x="85"/>
+        <item x="15"/>
+        <item x="63"/>
+        <item x="97"/>
+        <item x="42"/>
+        <item x="77"/>
+        <item x="109"/>
+        <item x="49"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="104"/>
+        <item x="44"/>
+        <item x="54"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="74"/>
+        <item x="53"/>
+        <item x="7"/>
+        <item x="35"/>
+        <item x="71"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="80"/>
+        <item x="61"/>
+        <item x="99"/>
+        <item x="67"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="39"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="103"/>
+        <item x="18"/>
+        <item x="76"/>
+        <item x="1"/>
+        <item x="96"/>
+        <item x="41"/>
+        <item x="14"/>
+        <item x="87"/>
+        <item x="29"/>
+        <item x="52"/>
+        <item x="58"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="16"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="94"/>
+        <item x="26"/>
+        <item x="89"/>
+        <item x="37"/>
+        <item x="90"/>
+        <item x="43"/>
+        <item x="105"/>
+        <item x="56"/>
+        <item x="106"/>
+        <item x="62"/>
+        <item x="88"/>
+        <item x="93"/>
+        <item x="108"/>
+        <item x="86"/>
+        <item x="68"/>
+        <item x="3"/>
+        <item x="69"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="discount%" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="10" filterVal="10"/>
         </filterColumn>
       </autoFilter>
     </filter>
@@ -26697,6 +27826,292 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDB06582-160B-4788-A911-CA10DFC396DA}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="L43:M48" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="PRODUCT COUNT" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94B2C9B9-4697-4B48-8B71-6C0F0E2C195F}" name="PivotTable17" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A51:D55" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="24">
+        <item x="22"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Average_reviews" fld="8" subtotal="average" baseField="6" baseItem="0" numFmtId="2"/>
+    <dataField name="Averag_rating" fld="10" subtotal="average" baseField="6" baseItem="0" numFmtId="164"/>
+    <dataField name="Average Discount %" fld="4" subtotal="average" baseField="6" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE53C5F1-C67D-46FB-B157-7DCD3927F593}" name="PivotTable16" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E32:F45" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -26929,407 +28344,6 @@
       </autoFilter>
     </filter>
   </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B3B400B-9577-4EEF-B566-A92C3E25FD68}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="121">
-        <item x="38"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="31"/>
-        <item x="60"/>
-        <item x="55"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="102"/>
-        <item x="79"/>
-        <item x="5"/>
-        <item x="101"/>
-        <item x="92"/>
-        <item x="47"/>
-        <item x="72"/>
-        <item x="65"/>
-        <item x="64"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="20"/>
-        <item x="95"/>
-        <item x="12"/>
-        <item x="40"/>
-        <item x="21"/>
-        <item x="57"/>
-        <item x="28"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="59"/>
-        <item x="107"/>
-        <item x="91"/>
-        <item x="45"/>
-        <item x="75"/>
-        <item x="70"/>
-        <item x="98"/>
-        <item x="100"/>
-        <item x="66"/>
-        <item x="85"/>
-        <item x="15"/>
-        <item x="63"/>
-        <item x="110"/>
-        <item x="114"/>
-        <item x="112"/>
-        <item x="111"/>
-        <item x="113"/>
-        <item x="115"/>
-        <item x="97"/>
-        <item x="42"/>
-        <item x="77"/>
-        <item x="109"/>
-        <item x="49"/>
-        <item x="46"/>
-        <item x="83"/>
-        <item x="104"/>
-        <item x="44"/>
-        <item x="54"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="74"/>
-        <item x="53"/>
-        <item x="7"/>
-        <item x="35"/>
-        <item x="71"/>
-        <item x="25"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="117"/>
-        <item x="116"/>
-        <item x="80"/>
-        <item x="61"/>
-        <item x="99"/>
-        <item x="67"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="39"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="103"/>
-        <item x="18"/>
-        <item x="119"/>
-        <item x="118"/>
-        <item x="76"/>
-        <item x="1"/>
-        <item x="96"/>
-        <item x="41"/>
-        <item x="14"/>
-        <item x="87"/>
-        <item x="29"/>
-        <item x="52"/>
-        <item x="58"/>
-        <item x="82"/>
-        <item x="84"/>
-        <item x="16"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="94"/>
-        <item x="26"/>
-        <item x="89"/>
-        <item x="37"/>
-        <item x="90"/>
-        <item x="43"/>
-        <item x="105"/>
-        <item x="56"/>
-        <item x="106"/>
-        <item x="62"/>
-        <item x="88"/>
-        <item x="93"/>
-        <item x="108"/>
-        <item x="86"/>
-        <item x="68"/>
-        <item x="3"/>
-        <item x="69"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="43">
-        <item x="38"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="39"/>
-        <item x="23"/>
-        <item x="30"/>
-        <item x="37"/>
-        <item x="36"/>
-        <item x="25"/>
-        <item x="24"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="22"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="44">
-        <item x="39"/>
-        <item x="41"/>
-        <item x="26"/>
-        <item x="34"/>
-        <item x="24"/>
-        <item x="38"/>
-        <item x="31"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="30"/>
-        <item x="36"/>
-        <item x="27"/>
-        <item x="35"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="40"/>
-        <item x="33"/>
-        <item x="37"/>
-        <item x="29"/>
-        <item x="22"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="ratings" fld="10" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22B681EE-FF7B-4954-B4E1-F46FE96FADCE}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="L53:M58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Product" fld="0" subtotal="count" baseField="11" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -27813,7 +28827,7 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="str" cm="1">
-        <f t="array" ref="L2">_xlfn.IFS(K2&lt;3,"POOR", K2&lt;4.5,"AVERAGE", K2&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L2">_xlfn.IFS(K2="","",K2&lt;3,"POOR", K2&lt;4.5,"AVERAGE", K2&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M2">
@@ -27861,7 +28875,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L3" t="str" cm="1">
-        <f t="array" ref="L3">_xlfn.IFS(K3&lt;3,"POOR", K3&lt;4.5,"AVERAGE", K3&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L3">_xlfn.IFS(K3="","",K3&lt;3,"POOR", K3&lt;4.5,"AVERAGE", K3&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M3">
@@ -27909,7 +28923,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L4" t="str" cm="1">
-        <f t="array" ref="L4">_xlfn.IFS(K4&lt;3,"POOR", K4&lt;4.5,"AVERAGE", K4&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L4">_xlfn.IFS(K4="","",K4&lt;3,"POOR", K4&lt;4.5,"AVERAGE", K4&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M4">
@@ -27957,7 +28971,7 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="str" cm="1">
-        <f t="array" ref="L5">_xlfn.IFS(K5&lt;3,"POOR", K5&lt;4.5,"AVERAGE", K5&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L5">_xlfn.IFS(K5="","",K5&lt;3,"POOR", K5&lt;4.5,"AVERAGE", K5&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M5">
@@ -28005,7 +29019,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="str" cm="1">
-        <f t="array" ref="L6">_xlfn.IFS(K6&lt;3,"POOR", K6&lt;4.5,"AVERAGE", K6&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L6">_xlfn.IFS(K6="","",K6&lt;3,"POOR", K6&lt;4.5,"AVERAGE", K6&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M6">
@@ -28053,7 +29067,7 @@
         <v>4</v>
       </c>
       <c r="L7" t="str" cm="1">
-        <f t="array" ref="L7">_xlfn.IFS(K7&lt;3,"POOR", K7&lt;4.5,"AVERAGE", K7&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L7">_xlfn.IFS(K7="","",K7&lt;3,"POOR", K7&lt;4.5,"AVERAGE", K7&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M7">
@@ -28101,7 +29115,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L8" t="str" cm="1">
-        <f t="array" ref="L8">_xlfn.IFS(K8&lt;3,"POOR", K8&lt;4.5,"AVERAGE", K8&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L8">_xlfn.IFS(K8="","",K8&lt;3,"POOR", K8&lt;4.5,"AVERAGE", K8&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M8">
@@ -28149,7 +29163,7 @@
         <v>4</v>
       </c>
       <c r="L9" t="str" cm="1">
-        <f t="array" ref="L9">_xlfn.IFS(K9&lt;3,"POOR", K9&lt;4.5,"AVERAGE", K9&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L9">_xlfn.IFS(K9="","",K9&lt;3,"POOR", K9&lt;4.5,"AVERAGE", K9&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M9">
@@ -28197,7 +29211,7 @@
         <v>4.8</v>
       </c>
       <c r="L10" t="str" cm="1">
-        <f t="array" ref="L10">_xlfn.IFS(K10&lt;3,"POOR", K10&lt;4.5,"AVERAGE", K10&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L10">_xlfn.IFS(K10="","",K10&lt;3,"POOR", K10&lt;4.5,"AVERAGE", K10&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M10">
@@ -28245,7 +29259,7 @@
         <v>3.8</v>
       </c>
       <c r="L11" t="str" cm="1">
-        <f t="array" ref="L11">_xlfn.IFS(K11&lt;3,"POOR", K11&lt;4.5,"AVERAGE", K11&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L11">_xlfn.IFS(K11="","",K11&lt;3,"POOR", K11&lt;4.5,"AVERAGE", K11&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M11">
@@ -28293,7 +29307,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L12" t="str" cm="1">
-        <f t="array" ref="L12">_xlfn.IFS(K12&lt;3,"POOR", K12&lt;4.5,"AVERAGE", K12&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L12">_xlfn.IFS(K12="","",K12&lt;3,"POOR", K12&lt;4.5,"AVERAGE", K12&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M12">
@@ -28341,7 +29355,7 @@
         <v>4.7</v>
       </c>
       <c r="L13" t="str" cm="1">
-        <f t="array" ref="L13">_xlfn.IFS(K13&lt;3,"POOR", K13&lt;4.5,"AVERAGE", K13&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L13">_xlfn.IFS(K13="","",K13&lt;3,"POOR", K13&lt;4.5,"AVERAGE", K13&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M13">
@@ -28389,7 +29403,7 @@
         <v>4.8</v>
       </c>
       <c r="L14" t="str" cm="1">
-        <f t="array" ref="L14">_xlfn.IFS(K14&lt;3,"POOR", K14&lt;4.5,"AVERAGE", K14&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L14">_xlfn.IFS(K14="","",K14&lt;3,"POOR", K14&lt;4.5,"AVERAGE", K14&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M14">
@@ -28437,7 +29451,7 @@
         <v>4.5</v>
       </c>
       <c r="L15" t="str" cm="1">
-        <f t="array" ref="L15">_xlfn.IFS(K15&lt;3,"POOR", K15&lt;4.5,"AVERAGE", K15&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L15">_xlfn.IFS(K15="","",K15&lt;3,"POOR", K15&lt;4.5,"AVERAGE", K15&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M15">
@@ -28485,7 +29499,7 @@
         <v>4.2</v>
       </c>
       <c r="L16" t="str" cm="1">
-        <f t="array" ref="L16">_xlfn.IFS(K16&lt;3,"POOR", K16&lt;4.5,"AVERAGE", K16&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L16">_xlfn.IFS(K16="","",K16&lt;3,"POOR", K16&lt;4.5,"AVERAGE", K16&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M16">
@@ -28533,7 +29547,7 @@
         <v>5</v>
       </c>
       <c r="L17" t="str" cm="1">
-        <f t="array" ref="L17">_xlfn.IFS(K17&lt;3,"POOR", K17&lt;4.5,"AVERAGE", K17&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L17">_xlfn.IFS(K17="","",K17&lt;3,"POOR", K17&lt;4.5,"AVERAGE", K17&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M17">
@@ -28581,7 +29595,7 @@
         <v>5</v>
       </c>
       <c r="L18" t="str" cm="1">
-        <f t="array" ref="L18">_xlfn.IFS(K18&lt;3,"POOR", K18&lt;4.5,"AVERAGE", K18&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L18">_xlfn.IFS(K18="","",K18&lt;3,"POOR", K18&lt;4.5,"AVERAGE", K18&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M18">
@@ -28629,7 +29643,7 @@
         <v>5</v>
       </c>
       <c r="L19" t="str" cm="1">
-        <f t="array" ref="L19">_xlfn.IFS(K19&lt;3,"POOR", K19&lt;4.5,"AVERAGE", K19&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L19">_xlfn.IFS(K19="","",K19&lt;3,"POOR", K19&lt;4.5,"AVERAGE", K19&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M19">
@@ -28677,7 +29691,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L20" t="str" cm="1">
-        <f t="array" ref="L20">_xlfn.IFS(K20&lt;3,"POOR", K20&lt;4.5,"AVERAGE", K20&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L20">_xlfn.IFS(K20="","",K20&lt;3,"POOR", K20&lt;4.5,"AVERAGE", K20&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M20">
@@ -28725,7 +29739,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L21" t="str" cm="1">
-        <f t="array" ref="L21">_xlfn.IFS(K21&lt;3,"POOR", K21&lt;4.5,"AVERAGE", K21&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L21">_xlfn.IFS(K21="","",K21&lt;3,"POOR", K21&lt;4.5,"AVERAGE", K21&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M21">
@@ -28773,7 +29787,7 @@
         <v>3.3</v>
       </c>
       <c r="L22" t="str" cm="1">
-        <f t="array" ref="L22">_xlfn.IFS(K22&lt;3,"POOR", K22&lt;4.5,"AVERAGE", K22&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L22">_xlfn.IFS(K22="","",K22&lt;3,"POOR", K22&lt;4.5,"AVERAGE", K22&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M22">
@@ -28815,8 +29829,8 @@
         <v/>
       </c>
       <c r="L23" t="str" cm="1">
-        <f t="array" ref="L23">_xlfn.IFS(K23&lt;3,"POOR", K23&lt;4.5,"AVERAGE", K23&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L23">_xlfn.IFS(K23="","",K23&lt;3,"POOR", K23&lt;4.5,"AVERAGE", K23&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="4"/>
@@ -28863,7 +29877,7 @@
         <v>4</v>
       </c>
       <c r="L24" t="str" cm="1">
-        <f t="array" ref="L24">_xlfn.IFS(K24&lt;3,"POOR", K24&lt;4.5,"AVERAGE", K24&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L24">_xlfn.IFS(K24="","",K24&lt;3,"POOR", K24&lt;4.5,"AVERAGE", K24&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M24">
@@ -28911,7 +29925,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L25" t="str" cm="1">
-        <f t="array" ref="L25">_xlfn.IFS(K25&lt;3,"POOR", K25&lt;4.5,"AVERAGE", K25&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L25">_xlfn.IFS(K25="","",K25&lt;3,"POOR", K25&lt;4.5,"AVERAGE", K25&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M25">
@@ -28959,7 +29973,7 @@
         <v>4.3</v>
       </c>
       <c r="L26" t="str" cm="1">
-        <f t="array" ref="L26">_xlfn.IFS(K26&lt;3,"POOR", K26&lt;4.5,"AVERAGE", K26&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L26">_xlfn.IFS(K26="","",K26&lt;3,"POOR", K26&lt;4.5,"AVERAGE", K26&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M26">
@@ -29007,7 +30021,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L27" t="str" cm="1">
-        <f t="array" ref="L27">_xlfn.IFS(K27&lt;3,"POOR", K27&lt;4.5,"AVERAGE", K27&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L27">_xlfn.IFS(K27="","",K27&lt;3,"POOR", K27&lt;4.5,"AVERAGE", K27&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M27">
@@ -29055,7 +30069,7 @@
         <v>3.8</v>
       </c>
       <c r="L28" t="str" cm="1">
-        <f t="array" ref="L28">_xlfn.IFS(K28&lt;3,"POOR", K28&lt;4.5,"AVERAGE", K28&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L28">_xlfn.IFS(K28="","",K28&lt;3,"POOR", K28&lt;4.5,"AVERAGE", K28&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M28">
@@ -29103,7 +30117,7 @@
         <v>3.8</v>
       </c>
       <c r="L29" t="str" cm="1">
-        <f t="array" ref="L29">_xlfn.IFS(K29&lt;3,"POOR", K29&lt;4.5,"AVERAGE", K29&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L29">_xlfn.IFS(K29="","",K29&lt;3,"POOR", K29&lt;4.5,"AVERAGE", K29&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M29">
@@ -29151,7 +30165,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L30" t="str" cm="1">
-        <f t="array" ref="L30">_xlfn.IFS(K30&lt;3,"POOR", K30&lt;4.5,"AVERAGE", K30&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L30">_xlfn.IFS(K30="","",K30&lt;3,"POOR", K30&lt;4.5,"AVERAGE", K30&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M30">
@@ -29193,8 +30207,8 @@
         <v/>
       </c>
       <c r="L31" t="str" cm="1">
-        <f t="array" ref="L31">_xlfn.IFS(K31&lt;3,"POOR", K31&lt;4.5,"AVERAGE", K31&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L31">_xlfn.IFS(K31="","",K31&lt;3,"POOR", K31&lt;4.5,"AVERAGE", K31&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="4"/>
@@ -29241,7 +30255,7 @@
         <v>4.3</v>
       </c>
       <c r="L32" t="str" cm="1">
-        <f t="array" ref="L32">_xlfn.IFS(K32&lt;3,"POOR", K32&lt;4.5,"AVERAGE", K32&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L32">_xlfn.IFS(K32="","",K32&lt;3,"POOR", K32&lt;4.5,"AVERAGE", K32&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M32">
@@ -29289,7 +30303,7 @@
         <v>4.7</v>
       </c>
       <c r="L33" t="str" cm="1">
-        <f t="array" ref="L33">_xlfn.IFS(K33&lt;3,"POOR", K33&lt;4.5,"AVERAGE", K33&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L33">_xlfn.IFS(K33="","",K33&lt;3,"POOR", K33&lt;4.5,"AVERAGE", K33&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M33">
@@ -29337,7 +30351,7 @@
         <v>4.3</v>
       </c>
       <c r="L34" t="str" cm="1">
-        <f t="array" ref="L34">_xlfn.IFS(K34&lt;3,"POOR", K34&lt;4.5,"AVERAGE", K34&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L34">_xlfn.IFS(K34="","",K34&lt;3,"POOR", K34&lt;4.5,"AVERAGE", K34&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M34">
@@ -29385,7 +30399,7 @@
         <v>4.7</v>
       </c>
       <c r="L35" t="str" cm="1">
-        <f t="array" ref="L35">_xlfn.IFS(K35&lt;3,"POOR", K35&lt;4.5,"AVERAGE", K35&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L35">_xlfn.IFS(K35="","",K35&lt;3,"POOR", K35&lt;4.5,"AVERAGE", K35&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M35">
@@ -29433,7 +30447,7 @@
         <v>4.5</v>
       </c>
       <c r="L36" t="str" cm="1">
-        <f t="array" ref="L36">_xlfn.IFS(K36&lt;3,"POOR", K36&lt;4.5,"AVERAGE", K36&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L36">_xlfn.IFS(K36="","",K36&lt;3,"POOR", K36&lt;4.5,"AVERAGE", K36&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M36">
@@ -29481,7 +30495,7 @@
         <v>5</v>
       </c>
       <c r="L37" t="str" cm="1">
-        <f t="array" ref="L37">_xlfn.IFS(K37&lt;3,"POOR", K37&lt;4.5,"AVERAGE", K37&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L37">_xlfn.IFS(K37="","",K37&lt;3,"POOR", K37&lt;4.5,"AVERAGE", K37&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M37">
@@ -29529,7 +30543,7 @@
         <v>5</v>
       </c>
       <c r="L38" t="str" cm="1">
-        <f t="array" ref="L38">_xlfn.IFS(K38&lt;3,"POOR", K38&lt;4.5,"AVERAGE", K38&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L38">_xlfn.IFS(K38="","",K38&lt;3,"POOR", K38&lt;4.5,"AVERAGE", K38&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M38">
@@ -29577,7 +30591,7 @@
         <v>4.3</v>
       </c>
       <c r="L39" t="str" cm="1">
-        <f t="array" ref="L39">_xlfn.IFS(K39&lt;3,"POOR", K39&lt;4.5,"AVERAGE", K39&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L39">_xlfn.IFS(K39="","",K39&lt;3,"POOR", K39&lt;4.5,"AVERAGE", K39&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M39">
@@ -29625,7 +30639,7 @@
         <v>4.5</v>
       </c>
       <c r="L40" t="str" cm="1">
-        <f t="array" ref="L40">_xlfn.IFS(K40&lt;3,"POOR", K40&lt;4.5,"AVERAGE", K40&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L40">_xlfn.IFS(K40="","",K40&lt;3,"POOR", K40&lt;4.5,"AVERAGE", K40&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M40">
@@ -29667,8 +30681,8 @@
         <v/>
       </c>
       <c r="L41" t="str" cm="1">
-        <f t="array" ref="L41">_xlfn.IFS(K41&lt;3,"POOR", K41&lt;4.5,"AVERAGE", K41&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L41">_xlfn.IFS(K41="","",K41&lt;3,"POOR", K41&lt;4.5,"AVERAGE", K41&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M41" t="str">
         <f t="shared" si="4"/>
@@ -29712,8 +30726,8 @@
         <v/>
       </c>
       <c r="L42" t="str" cm="1">
-        <f t="array" ref="L42">_xlfn.IFS(K42&lt;3,"POOR", K42&lt;4.5,"AVERAGE", K42&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L42">_xlfn.IFS(K42="","",K42&lt;3,"POOR", K42&lt;4.5,"AVERAGE", K42&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M42" t="str">
         <f t="shared" si="4"/>
@@ -29761,8 +30775,8 @@
         <v/>
       </c>
       <c r="L43" t="str" cm="1">
-        <f t="array" ref="L43">_xlfn.IFS(K43&lt;3,"POOR", K43&lt;4.5,"AVERAGE", K43&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L43">_xlfn.IFS(K43="","",K43&lt;3,"POOR", K43&lt;4.5,"AVERAGE", K43&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M43" t="str">
         <f t="shared" si="4"/>
@@ -29809,8 +30823,8 @@
         <v/>
       </c>
       <c r="L44" t="str" cm="1">
-        <f t="array" ref="L44">_xlfn.IFS(K44&lt;3,"POOR", K44&lt;4.5,"AVERAGE", K44&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L44">_xlfn.IFS(K44="","",K44&lt;3,"POOR", K44&lt;4.5,"AVERAGE", K44&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M44" t="str">
         <f t="shared" si="4"/>
@@ -29857,8 +30871,8 @@
         <v/>
       </c>
       <c r="L45" t="str" cm="1">
-        <f t="array" ref="L45">_xlfn.IFS(K45&lt;3,"POOR", K45&lt;4.5,"AVERAGE", K45&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L45">_xlfn.IFS(K45="","",K45&lt;3,"POOR", K45&lt;4.5,"AVERAGE", K45&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M45" t="str">
         <f t="shared" si="4"/>
@@ -29899,8 +30913,8 @@
         <v/>
       </c>
       <c r="L46" t="str" cm="1">
-        <f t="array" ref="L46">_xlfn.IFS(K46&lt;3,"POOR", K46&lt;4.5,"AVERAGE", K46&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L46">_xlfn.IFS(K46="","",K46&lt;3,"POOR", K46&lt;4.5,"AVERAGE", K46&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="4"/>
@@ -29941,8 +30955,8 @@
         <v/>
       </c>
       <c r="L47" t="str" cm="1">
-        <f t="array" ref="L47">_xlfn.IFS(K47&lt;3,"POOR", K47&lt;4.5,"AVERAGE", K47&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L47">_xlfn.IFS(K47="","",K47&lt;3,"POOR", K47&lt;4.5,"AVERAGE", K47&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="4"/>
@@ -29983,8 +30997,8 @@
         <v/>
       </c>
       <c r="L48" t="str" cm="1">
-        <f t="array" ref="L48">_xlfn.IFS(K48&lt;3,"POOR", K48&lt;4.5,"AVERAGE", K48&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L48">_xlfn.IFS(K48="","",K48&lt;3,"POOR", K48&lt;4.5,"AVERAGE", K48&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M48" t="str">
         <f t="shared" si="4"/>
@@ -30025,8 +31039,8 @@
         <v/>
       </c>
       <c r="L49" t="str" cm="1">
-        <f t="array" ref="L49">_xlfn.IFS(K49&lt;3,"POOR", K49&lt;4.5,"AVERAGE", K49&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L49">_xlfn.IFS(K49="","",K49&lt;3,"POOR", K49&lt;4.5,"AVERAGE", K49&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M49" t="str">
         <f t="shared" si="4"/>
@@ -30064,8 +31078,8 @@
         <v/>
       </c>
       <c r="L50" t="str" cm="1">
-        <f t="array" ref="L50">_xlfn.IFS(K50&lt;3,"POOR", K50&lt;4.5,"AVERAGE", K50&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L50">_xlfn.IFS(K50="","",K50&lt;3,"POOR", K50&lt;4.5,"AVERAGE", K50&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M50" t="str">
         <f t="shared" si="4"/>
@@ -30106,8 +31120,8 @@
         <v/>
       </c>
       <c r="L51" t="str" cm="1">
-        <f t="array" ref="L51">_xlfn.IFS(K51&lt;3,"POOR", K51&lt;4.5,"AVERAGE", K51&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L51">_xlfn.IFS(K51="","",K51&lt;3,"POOR", K51&lt;4.5,"AVERAGE", K51&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M51" t="str">
         <f t="shared" si="4"/>
@@ -30148,8 +31162,8 @@
         <v/>
       </c>
       <c r="L52" t="str" cm="1">
-        <f t="array" ref="L52">_xlfn.IFS(K52&lt;3,"POOR", K52&lt;4.5,"AVERAGE", K52&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L52">_xlfn.IFS(K52="","",K52&lt;3,"POOR", K52&lt;4.5,"AVERAGE", K52&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M52" t="str">
         <f t="shared" si="4"/>
@@ -30190,8 +31204,8 @@
         <v/>
       </c>
       <c r="L53" t="str" cm="1">
-        <f t="array" ref="L53">_xlfn.IFS(K53&lt;3,"POOR", K53&lt;4.5,"AVERAGE", K53&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L53">_xlfn.IFS(K53="","",K53&lt;3,"POOR", K53&lt;4.5,"AVERAGE", K53&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="4"/>
@@ -30232,8 +31246,8 @@
         <v/>
       </c>
       <c r="L54" t="str" cm="1">
-        <f t="array" ref="L54">_xlfn.IFS(K54&lt;3,"POOR", K54&lt;4.5,"AVERAGE", K54&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L54">_xlfn.IFS(K54="","",K54&lt;3,"POOR", K54&lt;4.5,"AVERAGE", K54&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M54" t="str">
         <f t="shared" si="4"/>
@@ -30274,8 +31288,8 @@
         <v/>
       </c>
       <c r="L55" t="str" cm="1">
-        <f t="array" ref="L55">_xlfn.IFS(K55&lt;3,"POOR", K55&lt;4.5,"AVERAGE", K55&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L55">_xlfn.IFS(K55="","",K55&lt;3,"POOR", K55&lt;4.5,"AVERAGE", K55&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M55" t="str">
         <f t="shared" si="4"/>
@@ -30313,8 +31327,8 @@
         <v/>
       </c>
       <c r="L56" t="str" cm="1">
-        <f t="array" ref="L56">_xlfn.IFS(K56&lt;3,"POOR", K56&lt;4.5,"AVERAGE", K56&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L56">_xlfn.IFS(K56="","",K56&lt;3,"POOR", K56&lt;4.5,"AVERAGE", K56&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="4"/>
@@ -30355,8 +31369,8 @@
         <v/>
       </c>
       <c r="L57" t="str" cm="1">
-        <f t="array" ref="L57">_xlfn.IFS(K57&lt;3,"POOR", K57&lt;4.5,"AVERAGE", K57&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L57">_xlfn.IFS(K57="","",K57&lt;3,"POOR", K57&lt;4.5,"AVERAGE", K57&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M57" t="str">
         <f t="shared" si="4"/>
@@ -30394,8 +31408,8 @@
         <v/>
       </c>
       <c r="L58" t="str" cm="1">
-        <f t="array" ref="L58">_xlfn.IFS(K58&lt;3,"POOR", K58&lt;4.5,"AVERAGE", K58&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L58">_xlfn.IFS(K58="","",K58&lt;3,"POOR", K58&lt;4.5,"AVERAGE", K58&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="4"/>
@@ -30436,8 +31450,8 @@
         <v/>
       </c>
       <c r="L59" t="str" cm="1">
-        <f t="array" ref="L59">_xlfn.IFS(K59&lt;3,"POOR", K59&lt;4.5,"AVERAGE", K59&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L59">_xlfn.IFS(K59="","",K59&lt;3,"POOR", K59&lt;4.5,"AVERAGE", K59&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M59" t="str">
         <f t="shared" si="4"/>
@@ -30478,8 +31492,8 @@
         <v/>
       </c>
       <c r="L60" t="str" cm="1">
-        <f t="array" ref="L60">_xlfn.IFS(K60&lt;3,"POOR", K60&lt;4.5,"AVERAGE", K60&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L60">_xlfn.IFS(K60="","",K60&lt;3,"POOR", K60&lt;4.5,"AVERAGE", K60&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M60" t="str">
         <f t="shared" si="4"/>
@@ -30526,7 +31540,7 @@
         <v>2.5</v>
       </c>
       <c r="L61" t="str" cm="1">
-        <f t="array" ref="L61">_xlfn.IFS(K61&lt;3,"POOR", K61&lt;4.5,"AVERAGE", K61&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L61">_xlfn.IFS(K61="","",K61&lt;3,"POOR", K61&lt;4.5,"AVERAGE", K61&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M61">
@@ -30574,7 +31588,7 @@
         <v>3</v>
       </c>
       <c r="L62" t="str" cm="1">
-        <f t="array" ref="L62">_xlfn.IFS(K62&lt;3,"POOR", K62&lt;4.5,"AVERAGE", K62&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L62">_xlfn.IFS(K62="","",K62&lt;3,"POOR", K62&lt;4.5,"AVERAGE", K62&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M62">
@@ -30622,7 +31636,7 @@
         <v>2.1</v>
       </c>
       <c r="L63" t="str" cm="1">
-        <f t="array" ref="L63">_xlfn.IFS(K63&lt;3,"POOR", K63&lt;4.5,"AVERAGE", K63&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L63">_xlfn.IFS(K63="","",K63&lt;3,"POOR", K63&lt;4.5,"AVERAGE", K63&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M63">
@@ -30670,7 +31684,7 @@
         <v>2.8</v>
       </c>
       <c r="L64" t="str" cm="1">
-        <f t="array" ref="L64">_xlfn.IFS(K64&lt;3,"POOR", K64&lt;4.5,"AVERAGE", K64&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L64">_xlfn.IFS(K64="","",K64&lt;3,"POOR", K64&lt;4.5,"AVERAGE", K64&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M64">
@@ -30718,7 +31732,7 @@
         <v>2.7</v>
       </c>
       <c r="L65" t="str" cm="1">
-        <f t="array" ref="L65">_xlfn.IFS(K65&lt;3,"POOR", K65&lt;4.5,"AVERAGE", K65&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L65">_xlfn.IFS(K65="","",K65&lt;3,"POOR", K65&lt;4.5,"AVERAGE", K65&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M65">
@@ -30766,7 +31780,7 @@
         <v>2.9</v>
       </c>
       <c r="L66" t="str" cm="1">
-        <f t="array" ref="L66">_xlfn.IFS(K66&lt;3,"POOR", K66&lt;4.5,"AVERAGE", K66&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L66">_xlfn.IFS(K66="","",K66&lt;3,"POOR", K66&lt;4.5,"AVERAGE", K66&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M66">
@@ -30814,7 +31828,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="L67" t="str" cm="1">
-        <f t="array" ref="L67">_xlfn.IFS(K67&lt;3,"POOR", K67&lt;4.5,"AVERAGE", K67&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L67">_xlfn.IFS(K67="","",K67&lt;3,"POOR", K67&lt;4.5,"AVERAGE", K67&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M67">
@@ -30862,7 +31876,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="L68" t="str" cm="1">
-        <f t="array" ref="L68">_xlfn.IFS(K68&lt;3,"POOR", K68&lt;4.5,"AVERAGE", K68&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L68">_xlfn.IFS(K68="","",K68&lt;3,"POOR", K68&lt;4.5,"AVERAGE", K68&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M68">
@@ -30910,7 +31924,7 @@
         <v>3</v>
       </c>
       <c r="L69" t="str" cm="1">
-        <f t="array" ref="L69">_xlfn.IFS(K69&lt;3,"POOR", K69&lt;4.5,"AVERAGE", K69&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L69">_xlfn.IFS(K69="","",K69&lt;3,"POOR", K69&lt;4.5,"AVERAGE", K69&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M69">
@@ -30958,7 +31972,7 @@
         <v>2.6</v>
       </c>
       <c r="L70" t="str" cm="1">
-        <f t="array" ref="L70">_xlfn.IFS(K70&lt;3,"POOR", K70&lt;4.5,"AVERAGE", K70&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L70">_xlfn.IFS(K70="","",K70&lt;3,"POOR", K70&lt;4.5,"AVERAGE", K70&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M70">
@@ -31006,7 +32020,7 @@
         <v>3</v>
       </c>
       <c r="L71" t="str" cm="1">
-        <f t="array" ref="L71">_xlfn.IFS(K71&lt;3,"POOR", K71&lt;4.5,"AVERAGE", K71&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L71">_xlfn.IFS(K71="","",K71&lt;3,"POOR", K71&lt;4.5,"AVERAGE", K71&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M71">
@@ -31054,7 +32068,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="L72" t="str" cm="1">
-        <f t="array" ref="L72">_xlfn.IFS(K72&lt;3,"POOR", K72&lt;4.5,"AVERAGE", K72&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L72">_xlfn.IFS(K72="","",K72&lt;3,"POOR", K72&lt;4.5,"AVERAGE", K72&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M72">
@@ -31102,7 +32116,7 @@
         <v>3</v>
       </c>
       <c r="L73" t="str" cm="1">
-        <f t="array" ref="L73">_xlfn.IFS(K73&lt;3,"POOR", K73&lt;4.5,"AVERAGE", K73&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L73">_xlfn.IFS(K73="","",K73&lt;3,"POOR", K73&lt;4.5,"AVERAGE", K73&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M73">
@@ -31150,7 +32164,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="L74" t="str" cm="1">
-        <f t="array" ref="L74">_xlfn.IFS(K74&lt;3,"POOR", K74&lt;4.5,"AVERAGE", K74&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L74">_xlfn.IFS(K74="","",K74&lt;3,"POOR", K74&lt;4.5,"AVERAGE", K74&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M74">
@@ -31198,7 +32212,7 @@
         <v>2.1</v>
       </c>
       <c r="L75" t="str" cm="1">
-        <f t="array" ref="L75">_xlfn.IFS(K75&lt;3,"POOR", K75&lt;4.5,"AVERAGE", K75&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L75">_xlfn.IFS(K75="","",K75&lt;3,"POOR", K75&lt;4.5,"AVERAGE", K75&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M75">
@@ -31240,8 +32254,8 @@
         <v/>
       </c>
       <c r="L76" t="str" cm="1">
-        <f t="array" ref="L76">_xlfn.IFS(K76&lt;3,"POOR", K76&lt;4.5,"AVERAGE", K76&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L76">_xlfn.IFS(K76="","",K76&lt;3,"POOR", K76&lt;4.5,"AVERAGE", K76&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M76" t="str">
         <f t="shared" si="9"/>
@@ -31282,8 +32296,8 @@
         <v/>
       </c>
       <c r="L77" t="str" cm="1">
-        <f t="array" ref="L77">_xlfn.IFS(K77&lt;3,"POOR", K77&lt;4.5,"AVERAGE", K77&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L77">_xlfn.IFS(K77="","",K77&lt;3,"POOR", K77&lt;4.5,"AVERAGE", K77&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M77" t="str">
         <f t="shared" si="9"/>
@@ -31324,8 +32338,8 @@
         <v/>
       </c>
       <c r="L78" t="str" cm="1">
-        <f t="array" ref="L78">_xlfn.IFS(K78&lt;3,"POOR", K78&lt;4.5,"AVERAGE", K78&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L78">_xlfn.IFS(K78="","",K78&lt;3,"POOR", K78&lt;4.5,"AVERAGE", K78&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M78" t="str">
         <f t="shared" si="9"/>
@@ -31366,8 +32380,8 @@
         <v/>
       </c>
       <c r="L79" t="str" cm="1">
-        <f t="array" ref="L79">_xlfn.IFS(K79&lt;3,"POOR", K79&lt;4.5,"AVERAGE", K79&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L79">_xlfn.IFS(K79="","",K79&lt;3,"POOR", K79&lt;4.5,"AVERAGE", K79&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M79" t="str">
         <f t="shared" si="9"/>
@@ -31414,7 +32428,7 @@
         <v>3</v>
       </c>
       <c r="L80" t="str" cm="1">
-        <f t="array" ref="L80">_xlfn.IFS(K80&lt;3,"POOR", K80&lt;4.5,"AVERAGE", K80&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L80">_xlfn.IFS(K80="","",K80&lt;3,"POOR", K80&lt;4.5,"AVERAGE", K80&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M80">
@@ -31462,7 +32476,7 @@
         <v>5</v>
       </c>
       <c r="L81" t="str" cm="1">
-        <f t="array" ref="L81">_xlfn.IFS(K81&lt;3,"POOR", K81&lt;4.5,"AVERAGE", K81&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L81">_xlfn.IFS(K81="","",K81&lt;3,"POOR", K81&lt;4.5,"AVERAGE", K81&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M81">
@@ -31504,8 +32518,8 @@
         <v/>
       </c>
       <c r="L82" t="str" cm="1">
-        <f t="array" ref="L82">_xlfn.IFS(K82&lt;3,"POOR", K82&lt;4.5,"AVERAGE", K82&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L82">_xlfn.IFS(K82="","",K82&lt;3,"POOR", K82&lt;4.5,"AVERAGE", K82&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="9"/>
@@ -31546,8 +32560,8 @@
         <v/>
       </c>
       <c r="L83" t="str" cm="1">
-        <f t="array" ref="L83">_xlfn.IFS(K83&lt;3,"POOR", K83&lt;4.5,"AVERAGE", K83&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L83">_xlfn.IFS(K83="","",K83&lt;3,"POOR", K83&lt;4.5,"AVERAGE", K83&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M83" t="str">
         <f t="shared" si="9"/>
@@ -31594,7 +32608,7 @@
         <v>4</v>
       </c>
       <c r="L84" t="str" cm="1">
-        <f t="array" ref="L84">_xlfn.IFS(K84&lt;3,"POOR", K84&lt;4.5,"AVERAGE", K84&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L84">_xlfn.IFS(K84="","",K84&lt;3,"POOR", K84&lt;4.5,"AVERAGE", K84&gt;=4.5,"EXCELLENT")</f>
         <v>AVERAGE</v>
       </c>
       <c r="M84">
@@ -31636,8 +32650,8 @@
         <v/>
       </c>
       <c r="L85" t="str" cm="1">
-        <f t="array" ref="L85">_xlfn.IFS(K85&lt;3,"POOR", K85&lt;4.5,"AVERAGE", K85&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L85">_xlfn.IFS(K85="","",K85&lt;3,"POOR", K85&lt;4.5,"AVERAGE", K85&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M85" t="str">
         <f t="shared" si="9"/>
@@ -31678,8 +32692,8 @@
         <v/>
       </c>
       <c r="L86" t="str" cm="1">
-        <f t="array" ref="L86">_xlfn.IFS(K86&lt;3,"POOR", K86&lt;4.5,"AVERAGE", K86&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L86">_xlfn.IFS(K86="","",K86&lt;3,"POOR", K86&lt;4.5,"AVERAGE", K86&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M86" t="str">
         <f t="shared" si="9"/>
@@ -31720,8 +32734,8 @@
         <v/>
       </c>
       <c r="L87" t="str" cm="1">
-        <f t="array" ref="L87">_xlfn.IFS(K87&lt;3,"POOR", K87&lt;4.5,"AVERAGE", K87&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L87">_xlfn.IFS(K87="","",K87&lt;3,"POOR", K87&lt;4.5,"AVERAGE", K87&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M87" t="str">
         <f t="shared" si="9"/>
@@ -31762,8 +32776,8 @@
         <v/>
       </c>
       <c r="L88" t="str" cm="1">
-        <f t="array" ref="L88">_xlfn.IFS(K88&lt;3,"POOR", K88&lt;4.5,"AVERAGE", K88&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L88">_xlfn.IFS(K88="","",K88&lt;3,"POOR", K88&lt;4.5,"AVERAGE", K88&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M88" t="str">
         <f t="shared" si="9"/>
@@ -31804,8 +32818,8 @@
         <v/>
       </c>
       <c r="L89" t="str" cm="1">
-        <f t="array" ref="L89">_xlfn.IFS(K89&lt;3,"POOR", K89&lt;4.5,"AVERAGE", K89&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L89">_xlfn.IFS(K89="","",K89&lt;3,"POOR", K89&lt;4.5,"AVERAGE", K89&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M89" t="str">
         <f t="shared" si="9"/>
@@ -31846,8 +32860,8 @@
         <v/>
       </c>
       <c r="L90" t="str" cm="1">
-        <f t="array" ref="L90">_xlfn.IFS(K90&lt;3,"POOR", K90&lt;4.5,"AVERAGE", K90&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L90">_xlfn.IFS(K90="","",K90&lt;3,"POOR", K90&lt;4.5,"AVERAGE", K90&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M90" t="str">
         <f t="shared" si="9"/>
@@ -31888,8 +32902,8 @@
         <v/>
       </c>
       <c r="L91" t="str" cm="1">
-        <f t="array" ref="L91">_xlfn.IFS(K91&lt;3,"POOR", K91&lt;4.5,"AVERAGE", K91&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L91">_xlfn.IFS(K91="","",K91&lt;3,"POOR", K91&lt;4.5,"AVERAGE", K91&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M91" t="str">
         <f t="shared" si="9"/>
@@ -31930,8 +32944,8 @@
         <v/>
       </c>
       <c r="L92" t="str" cm="1">
-        <f t="array" ref="L92">_xlfn.IFS(K92&lt;3,"POOR", K92&lt;4.5,"AVERAGE", K92&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L92">_xlfn.IFS(K92="","",K92&lt;3,"POOR", K92&lt;4.5,"AVERAGE", K92&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M92" t="str">
         <f t="shared" si="9"/>
@@ -31972,8 +32986,8 @@
         <v/>
       </c>
       <c r="L93" t="str" cm="1">
-        <f t="array" ref="L93">_xlfn.IFS(K93&lt;3,"POOR", K93&lt;4.5,"AVERAGE", K93&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L93">_xlfn.IFS(K93="","",K93&lt;3,"POOR", K93&lt;4.5,"AVERAGE", K93&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M93" t="str">
         <f t="shared" si="9"/>
@@ -32014,8 +33028,8 @@
         <v/>
       </c>
       <c r="L94" t="str" cm="1">
-        <f t="array" ref="L94">_xlfn.IFS(K94&lt;3,"POOR", K94&lt;4.5,"AVERAGE", K94&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L94">_xlfn.IFS(K94="","",K94&lt;3,"POOR", K94&lt;4.5,"AVERAGE", K94&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M94" t="str">
         <f t="shared" si="9"/>
@@ -32056,8 +33070,8 @@
         <v/>
       </c>
       <c r="L95" t="str" cm="1">
-        <f t="array" ref="L95">_xlfn.IFS(K95&lt;3,"POOR", K95&lt;4.5,"AVERAGE", K95&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L95">_xlfn.IFS(K95="","",K95&lt;3,"POOR", K95&lt;4.5,"AVERAGE", K95&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M95" t="str">
         <f t="shared" si="9"/>
@@ -32098,8 +33112,8 @@
         <v/>
       </c>
       <c r="L96" t="str" cm="1">
-        <f t="array" ref="L96">_xlfn.IFS(K96&lt;3,"POOR", K96&lt;4.5,"AVERAGE", K96&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L96">_xlfn.IFS(K96="","",K96&lt;3,"POOR", K96&lt;4.5,"AVERAGE", K96&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M96" t="str">
         <f t="shared" si="9"/>
@@ -32140,8 +33154,8 @@
         <v/>
       </c>
       <c r="L97" t="str" cm="1">
-        <f t="array" ref="L97">_xlfn.IFS(K97&lt;3,"POOR", K97&lt;4.5,"AVERAGE", K97&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L97">_xlfn.IFS(K97="","",K97&lt;3,"POOR", K97&lt;4.5,"AVERAGE", K97&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M97" t="str">
         <f t="shared" si="9"/>
@@ -32182,8 +33196,8 @@
         <v/>
       </c>
       <c r="L98" t="str" cm="1">
-        <f t="array" ref="L98">_xlfn.IFS(K98&lt;3,"POOR", K98&lt;4.5,"AVERAGE", K98&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L98">_xlfn.IFS(K98="","",K98&lt;3,"POOR", K98&lt;4.5,"AVERAGE", K98&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M98" t="str">
         <f t="shared" si="9"/>
@@ -32224,8 +33238,8 @@
         <v/>
       </c>
       <c r="L99" t="str" cm="1">
-        <f t="array" ref="L99">_xlfn.IFS(K99&lt;3,"POOR", K99&lt;4.5,"AVERAGE", K99&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L99">_xlfn.IFS(K99="","",K99&lt;3,"POOR", K99&lt;4.5,"AVERAGE", K99&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M99" t="str">
         <f t="shared" si="9"/>
@@ -32266,8 +33280,8 @@
         <v/>
       </c>
       <c r="L100" t="str" cm="1">
-        <f t="array" ref="L100">_xlfn.IFS(K100&lt;3,"POOR", K100&lt;4.5,"AVERAGE", K100&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L100">_xlfn.IFS(K100="","",K100&lt;3,"POOR", K100&lt;4.5,"AVERAGE", K100&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M100" t="str">
         <f t="shared" si="9"/>
@@ -32308,8 +33322,8 @@
         <v/>
       </c>
       <c r="L101" t="str" cm="1">
-        <f t="array" ref="L101">_xlfn.IFS(K101&lt;3,"POOR", K101&lt;4.5,"AVERAGE", K101&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L101">_xlfn.IFS(K101="","",K101&lt;3,"POOR", K101&lt;4.5,"AVERAGE", K101&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M101" t="str">
         <f t="shared" si="9"/>
@@ -32350,8 +33364,8 @@
         <v/>
       </c>
       <c r="L102" t="str" cm="1">
-        <f t="array" ref="L102">_xlfn.IFS(K102&lt;3,"POOR", K102&lt;4.5,"AVERAGE", K102&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L102">_xlfn.IFS(K102="","",K102&lt;3,"POOR", K102&lt;4.5,"AVERAGE", K102&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M102" t="str">
         <f t="shared" si="9"/>
@@ -32398,7 +33412,7 @@
         <v>5</v>
       </c>
       <c r="L103" t="str" cm="1">
-        <f t="array" ref="L103">_xlfn.IFS(K103&lt;3,"POOR", K103&lt;4.5,"AVERAGE", K103&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L103">_xlfn.IFS(K103="","",K103&lt;3,"POOR", K103&lt;4.5,"AVERAGE", K103&gt;=4.5,"EXCELLENT")</f>
         <v>EXCELLENT</v>
       </c>
       <c r="M103">
@@ -32440,8 +33454,8 @@
         <v/>
       </c>
       <c r="L104" t="str" cm="1">
-        <f t="array" ref="L104">_xlfn.IFS(K104&lt;3,"POOR", K104&lt;4.5,"AVERAGE", K104&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L104">_xlfn.IFS(K104="","",K104&lt;3,"POOR", K104&lt;4.5,"AVERAGE", K104&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M104" t="str">
         <f t="shared" si="9"/>
@@ -32482,8 +33496,8 @@
         <v/>
       </c>
       <c r="L105" t="str" cm="1">
-        <f t="array" ref="L105">_xlfn.IFS(K105&lt;3,"POOR", K105&lt;4.5,"AVERAGE", K105&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L105">_xlfn.IFS(K105="","",K105&lt;3,"POOR", K105&lt;4.5,"AVERAGE", K105&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M105" t="str">
         <f t="shared" si="9"/>
@@ -32524,8 +33538,8 @@
         <v/>
       </c>
       <c r="L106" t="str" cm="1">
-        <f t="array" ref="L106">_xlfn.IFS(K106&lt;3,"POOR", K106&lt;4.5,"AVERAGE", K106&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L106">_xlfn.IFS(K106="","",K106&lt;3,"POOR", K106&lt;4.5,"AVERAGE", K106&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M106" t="str">
         <f t="shared" si="9"/>
@@ -32566,8 +33580,8 @@
         <v/>
       </c>
       <c r="L107" t="str" cm="1">
-        <f t="array" ref="L107">_xlfn.IFS(K107&lt;3,"POOR", K107&lt;4.5,"AVERAGE", K107&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L107">_xlfn.IFS(K107="","",K107&lt;3,"POOR", K107&lt;4.5,"AVERAGE", K107&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M107" t="str">
         <f t="shared" si="9"/>
@@ -32608,8 +33622,8 @@
         <v/>
       </c>
       <c r="L108" t="str" cm="1">
-        <f t="array" ref="L108">_xlfn.IFS(K108&lt;3,"POOR", K108&lt;4.5,"AVERAGE", K108&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L108">_xlfn.IFS(K108="","",K108&lt;3,"POOR", K108&lt;4.5,"AVERAGE", K108&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M108" t="str">
         <f t="shared" si="9"/>
@@ -32650,8 +33664,8 @@
         <v/>
       </c>
       <c r="L109" t="str" cm="1">
-        <f t="array" ref="L109">_xlfn.IFS(K109&lt;3,"POOR", K109&lt;4.5,"AVERAGE", K109&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L109">_xlfn.IFS(K109="","",K109&lt;3,"POOR", K109&lt;4.5,"AVERAGE", K109&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M109" t="str">
         <f t="shared" si="9"/>
@@ -32692,8 +33706,8 @@
         <v/>
       </c>
       <c r="L110" t="str" cm="1">
-        <f t="array" ref="L110">_xlfn.IFS(K110&lt;3,"POOR", K110&lt;4.5,"AVERAGE", K110&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L110">_xlfn.IFS(K110="","",K110&lt;3,"POOR", K110&lt;4.5,"AVERAGE", K110&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M110" t="str">
         <f t="shared" si="9"/>
@@ -32734,8 +33748,8 @@
         <v/>
       </c>
       <c r="L111" t="str" cm="1">
-        <f t="array" ref="L111">_xlfn.IFS(K111&lt;3,"POOR", K111&lt;4.5,"AVERAGE", K111&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L111">_xlfn.IFS(K111="","",K111&lt;3,"POOR", K111&lt;4.5,"AVERAGE", K111&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M111" t="str">
         <f t="shared" si="9"/>
@@ -32782,7 +33796,7 @@
         <v>2</v>
       </c>
       <c r="L112" t="str" cm="1">
-        <f t="array" ref="L112">_xlfn.IFS(K112&lt;3,"POOR", K112&lt;4.5,"AVERAGE", K112&gt;=4.5,"EXCELLENT")</f>
+        <f t="array" ref="L112">_xlfn.IFS(K112="","",K112&lt;3,"POOR", K112&lt;4.5,"AVERAGE", K112&gt;=4.5,"EXCELLENT")</f>
         <v>POOR</v>
       </c>
       <c r="M112">
@@ -32824,8 +33838,8 @@
         <v/>
       </c>
       <c r="L113" t="str" cm="1">
-        <f t="array" ref="L113">_xlfn.IFS(K113&lt;3,"POOR", K113&lt;4.5,"AVERAGE", K113&gt;=4.5,"EXCELLENT")</f>
-        <v>EXCELLENT</v>
+        <f t="array" ref="L113">_xlfn.IFS(K113="","",K113&lt;3,"POOR", K113&lt;4.5,"AVERAGE", K113&gt;=4.5,"EXCELLENT")</f>
+        <v/>
       </c>
       <c r="M113" t="str">
         <f t="shared" si="9"/>
@@ -33755,13 +34769,13 @@
       <c r="A33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33">
         <v>39</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33">
         <v>2</v>
       </c>
     </row>
@@ -33769,13 +34783,13 @@
       <c r="A34" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34">
         <v>69</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34">
         <v>2</v>
       </c>
     </row>
@@ -33783,13 +34797,13 @@
       <c r="A35" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35">
         <v>55</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35">
         <v>2</v>
       </c>
     </row>
@@ -33797,13 +34811,13 @@
       <c r="A36" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36">
         <v>44</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36">
         <v>1</v>
       </c>
     </row>
@@ -33811,13 +34825,13 @@
       <c r="A37" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37">
         <v>20</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F37">
         <v>2</v>
       </c>
     </row>
@@ -33825,13 +34839,13 @@
       <c r="A38" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38">
         <v>32</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38">
         <v>2</v>
       </c>
     </row>
@@ -33839,13 +34853,13 @@
       <c r="A39" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39">
         <v>20</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39">
         <v>1</v>
       </c>
     </row>
@@ -33853,13 +34867,13 @@
       <c r="A40" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40">
         <v>49</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40">
         <v>1</v>
       </c>
     </row>
@@ -33867,13 +34881,13 @@
       <c r="A41" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41">
         <v>24</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41">
         <v>1</v>
       </c>
     </row>
@@ -33881,13 +34895,13 @@
       <c r="A42" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42">
         <v>36</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42">
         <v>1</v>
       </c>
     </row>
@@ -33895,13 +34909,13 @@
       <c r="A43" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43">
         <v>38.799999999999997</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43">
         <v>2</v>
       </c>
       <c r="L43" s="16" t="s">
@@ -33915,7 +34929,7 @@
       <c r="E44" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44">
         <v>1</v>
       </c>
       <c r="L44" s="17" t="s">
@@ -33929,7 +34943,7 @@
       <c r="E45" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45">
         <v>1.5</v>
       </c>
       <c r="L45" s="17" t="s">
